--- a/tests/e2e/content-import/fixtures/09_questions.xlsx
+++ b/tests/e2e/content-import/fixtures/09_questions.xlsx
@@ -34,7 +34,7 @@
     <t>correct_index</t>
   </si>
   <si>
-    <t>e2e-q-01</t>
+    <t>e2e-q-blocked-01</t>
   </si>
   <si>
     <t>e2e-sub-01</t>

--- a/tests/e2e/content-import/fixtures/09_questions.xlsx
+++ b/tests/e2e/content-import/fixtures/09_questions.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>question_code</t>
   </si>
@@ -34,7 +34,10 @@
     <t>correct_index</t>
   </si>
   <si>
-    <t>e2e-q-blocked-01</t>
+    <t>explanation</t>
+  </si>
+  <si>
+    <t>e2e-qi-01</t>
   </si>
   <si>
     <t>e2e-sub-01</t>
@@ -43,13 +46,31 @@
     <t>e2e-lesson-01</t>
   </si>
   <si>
-    <t>سؤال تجريبي؟</t>
+    <t>سؤال مستورد تجريبي أ؟</t>
   </si>
   <si>
     <t>خيار أ</t>
   </si>
   <si>
     <t>خيار ب</t>
+  </si>
+  <si>
+    <t>شرح الإجابة أ</t>
+  </si>
+  <si>
+    <t>e2e-qi-02</t>
+  </si>
+  <si>
+    <t>سؤال مستورد تجريبي ب؟</t>
+  </si>
+  <si>
+    <t>خيار 1</t>
+  </si>
+  <si>
+    <t>خيار 2</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -426,10 +447,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -451,28 +472,60 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2">
         <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
